--- a/demo/src/main/assets/samples/sample.xlsx
+++ b/demo/src/main/assets/samples/sample.xlsx
@@ -30,7 +30,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color rgb="FF202124"/>
@@ -42,8 +42,16 @@
       <u/>
       <color rgb="FFFFFFFF"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -60,8 +68,28 @@
         <fgColor rgb="FFE4F0F5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0000FF" tint="0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0000FF" tint="0.5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0000FF" tint="-0.5"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border/>
     <border>
       <left style="thin">
@@ -77,11 +105,25 @@
         <color rgb="FF112233"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="2"/>
+      </left>
+      <top style="thin">
+        <color indexed="2"/>
+      </top>
+      <right style="thin">
+        <color indexed="2"/>
+      </right>
+      <bottom style="thin">
+        <color indexed="2"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -97,7 +139,26 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf fontId="2" fillId="4" borderId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="3" fillId="5">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="6">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="3" fillId="7">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00202080"/>
+      <rgbColor rgb="00A0E0C0"/>
+      <rgbColor rgb="00800040"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -160,11 +221,95 @@
         </is>
       </c>
     </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">调色板与明暗色｜B 实际 · C 预期</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">自定义调色板
+字体 / 填充 / 边框</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Palette 调色板</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">深蓝字 · 浅绿底
+四边为紫红色</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">蓝色原色
+tint = 0</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">原色 Blue</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#0000FF
+作为明暗比较基准</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">提高明度
+tint = +0.5</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">变亮 Lighter</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#8080FF
+蓝色变浅，接近白色</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">降低明度
+tint = -0.5</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">变暗 Darker</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#000080
+蓝色变深，接近黑色</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A7:C7"/>
   </mergeCells>
 </worksheet>
 </file>
